--- a/League_Known_Data_Issues.xlsx
+++ b/League_Known_Data_Issues.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Known Issues" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks Passed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Known Issues'!$A$6:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Known Issues'!$A$6:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks Passed'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -520,6 +521,13 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Version 1.1, updated 18 Oct 2026: added LD-18 and LD-19, appended a decision to LD-11. Original findings unchanged. See the Change Log tab.</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1135,7 +1143,8 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Raise as a clarifying question for the recruiter, as the brief invites.</t>
+          <t>Raise as a clarifying question for the recruiter, as the brief invites.
+[Updated 18 Oct 2026, see Change Log] Decision: keep Government in ICP. The real League names government and public healthcare systems as a growth segment (League press release, 3 Sep 2025), and here Government produced 13 SQLs and a $793K win. Show Broker / Consultant separately as influencers, not as ICP buyers. No recruiter question planned; the choice is disclosed as an assumption in the analysis.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1459,47 +1468,47 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>LD-18</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Leads vs. Spend notes</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>month, channel, spend_usd</t>
+          <t>utm_source, utm_medium, utm_campaign, channel_reported (LinkedIn)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Data defect</t>
+          <t>Cross-file observation</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Content Syndication for 2025-11 appears twice ($8,125 each); the second row is noted "re-keyed from vendor statement". The file has 73 rows instead of 72 (6 channels x 12 months).</t>
+          <t>LinkedIn tracking loss lines up with the 9 Feb 2026 landing page migration. 35 LinkedIn leads created 24 Jan to 20 Apr 2026 have no UTMs and a blank or "Unknown" channel. LinkedIn leads before 24 Jan and from May onward are fully tagged.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>1 row ($8,125)</t>
+          <t>35 (all LinkedIn)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Raw total $575,124.99. Without the duplicate: $566,999.99, matching the brief's "about $567,000".</t>
+          <t>LinkedIn leads with no UTM by month: Jan 2 of 17, Feb 17 of 18, Mar 9 of 9, Apr 7 of 10, May and Jun 0. 7 of the 35 predate 9 Feb. LinkedIn spend notes for Feb to Apr read "landing page template migrated 09-Feb". campaign_name is intact on all 35. LinkedIn SQL rate fell from 22% (before 9 Feb) to 16% (after), but other channels fell further (15% to 8%), so the dip is consistent with cohort lag (LD-15), not lower lead quality.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Overstates Syndication spend and total FY26 spend.</t>
+          <t>Reports built on channel_reported or UTMs undercount LinkedIn by 35 leads (about 22% of its 156) during Feb to Apr, the months it received more spend. Explains all of LD-02's blank/Unknown rows and the 35 LinkedIn rows in LD-03. The new template likely dropped UTM pass-through; the start about two weeks before 9 Feb suggests a staged rollout (inference).</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Remove the duplicate row.</t>
+          <t>Attribute channel by campaign_name, which recovers all 35. Do not read the post-migration conversion dip as a channel-quality signal. Going forward, add a UTM / hidden-field check to every landing page release.</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -1511,59 +1520,59 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>LD-19</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Spend vs. README</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>spend_usd (Events, 2026-03)</t>
+          <t>spend_usd (period totals)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Data defect</t>
+          <t>Cross-file observation</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Events spend for March 2026 is blank; note reads "invoice not yet received from agency".</t>
+          <t>The README calls the $280,000 H1 FY27 budget "flat on H2 FY26", but H2 FY26 (Jan to Jun 2026) spend in the file is $286,395.82, and that excludes the blank March 2026 Events month (SP-02). H1 FY26 (Jul to Dec 2025) is $280,604.17 once the duplicate row (SP-01) is removed, a much closer match to $280K.</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>1 row</t>
+          <t>Whole file (period totals)</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>The brief's ~$567K matches only without this month, so true FY26 spend is likely higher. 3 Events leads were created in March.</t>
+          <t>H1 FY26 raw $288,729.17, less the $8,125 duplicate = $280,604.17. H2 FY26 = $286,395.82 with one blank Events month. Combined $566,999.99, matching the brief.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Understates Events spend, so Events cost per lead or SQL is understated.</t>
+          <t>H1 FY27 is at least about 2% below the H2 FY26 run rate, and more once March Events is invoiced, so "flat" overstates the budget against the period it names. The README may have meant H1 FY26, the same season last year (inference). Affects how targets compare with prior output.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Keep blank and disclose, or add a clearly labelled estimate. Do not silently fill with zero.</t>
+          <t>Treat $280K as a fixed budget rather than "flat". Benchmark the plan against H1 FY26 actuals (same season) and disclose the H2 gap as a stated assumption.</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>SP-03</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1573,7 +1582,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>spend_usd</t>
+          <t>month, channel, spend_usd</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1583,39 +1592,39 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Syndication ($8,125.00), Demandbase ($5,416.67) and Google Demand Gen ($4,583.33) show the same amount every month.</t>
+          <t>Content Syndication for 2025-11 appears twice ($8,125 each); the second row is noted "re-keyed from vendor statement". The file has 73 rows instead of 72 (6 channels x 12 months).</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>3 channels, 36 rows</t>
+          <t>1 row ($8,125)</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Google Demand Gen clicks swing from 2,185 (Apr) to 22,435 (Oct) on identical spend.</t>
+          <t>Raw total $575,124.99. Without the duplicate: $566,999.99, matching the brief's "about $567,000".</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>These look like straight-lined or allocated figures, not invoiced actuals (inference). Monthly cost trends and cost per click for these channels are not meaningful.</t>
+          <t>Overstates Syndication spend and total FY26 spend.</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Use totals by channel, not monthly trends, for these three.</t>
+          <t>Remove the duplicate row.</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1625,37 +1634,37 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>campaign_group</t>
+          <t>spend_usd (Events, 2026-03)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Definition conflict</t>
+          <t>Data defect</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Google Demand Gen, LinkedIn, Events and Webinars are "All campaigns (rolled up)". Only Syndication and Demandbase have campaign-level spend.</t>
+          <t>Events spend for March 2026 is blank; note reads "invoice not yet received from agency".</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>48 rows</t>
+          <t>1 row</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>The leads file has 12 campaigns: 2 GDG, 3 LinkedIn, 3 Events, 2 Webinar, 1 Syndication, 1 Demandbase.</t>
+          <t>The brief's ~$567K matches only without this month, so true FY26 spend is likely higher. 3 Events leads were created in March.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Cost per SQL by campaign is only possible for Syndication and Demandbase; elsewhere needs an allocation assumption.</t>
+          <t>Understates Events spend, so Events cost per lead or SQL is understated.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Work at the channel level. Avoid campaign-level cost claims.</t>
+          <t>Keep blank and disclose, or add a clearly labelled estimate. Do not silently fill with zero.</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -1667,7 +1676,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-03</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1677,49 +1686,49 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>spend_usd (Events)</t>
+          <t>spend_usd</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Analytical caveat</t>
+          <t>Data defect</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Events spend is lumpy: $26,000 in Sep and $31,000 in Oct 2025, $2,000 to $11,000 in other months.</t>
+          <t>Syndication ($8,125.00), Demandbase ($5,416.67) and Google Demand Gen ($4,583.33) show the same amount every month.</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>12 rows</t>
+          <t>3 channels, 36 rows</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Leads are dated daily; spend is booked monthly.</t>
+          <t>Google Demand Gen clicks swing from 2,185 (Apr) to 22,435 (Oct) on identical spend.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Matching event spend to leads by month will mis-time cause and effect.</t>
+          <t>These look like straight-lined or allocated figures, not invoiced actuals (inference). Monthly cost trends and cost per click for these channels are not meaningful.</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Compare Events on FY totals, not by month.</t>
+          <t>Use totals by channel, not monthly trends, for these three.</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SP-06</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1729,99 +1738,203 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>spend_usd</t>
+          <t>campaign_group</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Analytical caveat</t>
+          <t>Definition conflict</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Media spend only: excludes headcount, agency retainers and tooling (README).</t>
+          <t>Google Demand Gen, LinkedIn, Events and Webinars are "All campaigns (rolled up)". Only Syndication and Demandbase have campaign-level spend.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Whole file</t>
+          <t>48 rows</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Stated in the README.</t>
+          <t>The leads file has 12 campaigns: 2 GDG, 3 LinkedIn, 3 Events, 2 Webinar, 1 Syndication, 1 Demandbase.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Fully loaded cost per SQL is higher than the file implies, more so for labour-heavy channels like Events and Webinars (inference).</t>
+          <t>Cost per SQL by campaign is only possible for Syndication and Demandbase; elsewhere needs an allocation assumption.</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>State that cost figures are media-only.</t>
+          <t>Work at the channel level. Avoid campaign-level cost claims.</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>SP-05</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>spend_usd (Events)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Analytical caveat</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Events spend is lumpy: $26,000 in Sep and $31,000 in Oct 2025, $2,000 to $11,000 in other months.</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>12 rows</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Leads are dated daily; spend is booked monthly.</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Matching event spend to leads by month will mis-time cause and effect.</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Compare Events on FY totals, not by month.</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>SP-06</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>spend_usd</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Analytical caveat</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Media spend only: excludes headcount, agency retainers and tooling (README).</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Whole file</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Stated in the README.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Fully loaded cost per SQL is higher than the file implies, more so for labour-heavy channels like Events and Webinars (inference).</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>State that cost figures are media-only.</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>SP-07</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>impressions, clicks</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Analytical caveat</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Populated for Google Demand Gen and LinkedIn only.</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>48 rows blank</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Stated in the README.</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>No engagement-cost comparison across all six channels.</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>Compare channels on leads and SQLs, not clicks.</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:J30"/>
+  <autoFilter ref="A6:J32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2062,4 +2175,232 @@
   <autoFilter ref="A4:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>League Growth Marketing Data Package: Change Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every change to this workbook after the original findings. Original text is never deleted; updates are appended and dated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Made by</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 (earlier session)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>LD-01 to LD-17, SP-01 to SP-07</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Original findings and Checks Passed tab.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Baseline review of the FY26 data package.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Simon, with Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>LD-18</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Added: LinkedIn UTM and channel loss tied to the 9 Feb 2026 landing page migration.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Found during Part 2 planning. Links LD-02 and LD-03 to the migration noted in the README. Also corrects an earlier working assumption that LinkedIn conversion fell because of the migration; the dip matches cohort lag on every channel.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Drafted by Claude, approved by Simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>LD-19</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Added: H1 FY27 budget is not "flat" against H2 FY26 spend in the file.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Found during Part 2 planning. Affects the baseline used to judge the targets.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Drafted by Claude, approved by Simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>LD-11</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Appended a dated decision to "Options for handling": keep Government in ICP; show Broker / Consultant separately. Original text kept.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Real League go-to-market includes government and public health systems; decision disclosed as an assumption instead of a recruiter question.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Drafted by Claude, approved by Simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Header, Change Log</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Added a version note (row 5) and this Change Log tab. Filter range extended to the new rows.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Keep a visible history of changes.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Drafted by Claude, approved by Simon</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>